--- a/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-1102_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19786,7 +19786,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CHUNIZA-FAMACO-1102_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,11 +6036,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6132,7 +6044,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,11 +6285,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6385,7 +6293,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,11 +6534,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6638,7 +6542,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6879,11 +6783,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -6891,7 +6791,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7132,11 +7032,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7144,7 +7040,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7385,11 +7281,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7397,7 +7289,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7638,11 +7530,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7650,7 +7538,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7891,11 +7779,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -7903,7 +7787,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8144,11 +8028,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8156,7 +8036,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8397,11 +8277,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8409,7 +8285,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8650,11 +8526,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8662,7 +8534,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8899,11 +8771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -8911,7 +8779,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9152,11 +9020,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9164,7 +9028,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9405,11 +9269,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9417,7 +9277,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9670,7 +9526,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -9923,7 +9775,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10176,7 +10024,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10417,11 +10265,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10429,7 +10273,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10670,11 +10514,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10682,7 +10522,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10923,11 +10763,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -10935,7 +10771,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11176,11 +11012,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11188,7 +11020,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11429,11 +11261,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11441,7 +11269,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11682,11 +11510,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11694,7 +11518,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11935,11 +11759,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -11947,7 +11767,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12188,11 +12008,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12200,7 +12016,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12441,11 +12257,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12453,7 +12265,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12694,11 +12506,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12706,7 +12514,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12947,11 +12755,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -12959,7 +12763,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13200,11 +13004,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13212,7 +13012,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13453,11 +13253,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13465,7 +13261,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13706,11 +13502,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13718,7 +13510,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13959,11 +13751,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -13971,7 +13759,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14212,11 +14000,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14224,7 +14008,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14465,11 +14249,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14477,7 +14257,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14718,11 +14498,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14730,7 +14506,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14971,11 +14747,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -14983,7 +14755,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15224,11 +14996,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -15236,7 +15004,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15477,11 +15245,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -15489,7 +15253,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15730,11 +15494,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -15742,7 +15502,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15983,11 +15743,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -15995,7 +15751,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16236,11 +15992,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -16248,7 +16000,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16489,11 +16241,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -16501,7 +16249,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16742,11 +16490,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -16754,7 +16498,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16995,11 +16739,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -17007,7 +16747,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17248,11 +16988,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -17260,7 +16996,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17497,11 +17233,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -17509,7 +17241,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17750,11 +17482,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -17762,7 +17490,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -18003,11 +17731,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -18015,7 +17739,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18256,11 +17980,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -18268,7 +17988,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18509,11 +18229,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -18521,7 +18237,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18762,11 +18478,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -18774,7 +18486,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -19015,11 +18727,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -19027,7 +18735,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19268,11 +18976,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -19280,7 +18984,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19521,11 +19225,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -19533,7 +19233,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19774,11 +19474,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001098850</t>
@@ -19786,7 +19482,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CHUNIZA FAMACO (IED)</t>
+          <t>COLEGIO CHUNIZA FAMACO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
